--- a/phy115/Grades/grades_report_2026.xlsx
+++ b/phy115/Grades/grades_report_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ptohos/Documents/MyCourses/FYS115/2026/Grades/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81B3F4F0-4E50-4241-9843-AD32F650BA32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5A8BD3-372A-4E4C-93B7-8F6F6910D68E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5260" yWindow="9720" windowWidth="25240" windowHeight="11740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5260" yWindow="9720" windowWidth="25240" windowHeight="11740" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quizzes" sheetId="5" r:id="rId1"/>
@@ -1053,7 +1053,7 @@
         <v>2476</v>
       </c>
       <c r="B10" s="19">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="19"/>
@@ -1065,7 +1065,7 @@
       <c r="J10" s="19"/>
       <c r="K10" s="21">
         <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1213,7 +1213,7 @@
         <v>3466</v>
       </c>
       <c r="B18" s="19">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="C18" s="19"/>
       <c r="D18" s="19"/>
@@ -1225,7 +1225,7 @@
       <c r="J18" s="19"/>
       <c r="K18" s="21">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="B28" s="14">
         <f>AVERAGE(B$2:B$25)</f>
-        <v>9.3636363636363633</v>
+        <v>9.6136363636363633</v>
       </c>
       <c r="C28" s="14" t="e">
         <f t="shared" ref="C28:J28" si="1">AVERAGE(C$2:C$25)</f>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="B29" s="14">
         <f>STDEV(B$2:B$25)</f>
-        <v>4.5097297410889636</v>
+        <v>4.6596847895176703</v>
       </c>
       <c r="C29" s="14" t="e">
         <f t="shared" ref="C29:J29" si="2">STDEV(C$2:C$25)</f>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="B30" s="14">
         <f>MEDIAN(B$2:B$25)</f>
-        <v>10.5</v>
+        <v>10.75</v>
       </c>
       <c r="C30" s="14" t="e">
         <f t="shared" ref="C30:J30" si="3">MEDIAN(C$2:C$25)</f>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="B11" s="39">
         <f>Quizzes!K10</f>
-        <v>1.1000000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="C11" s="40">
         <f>Presentations!L10</f>
@@ -3735,11 +3735,11 @@
       </c>
       <c r="F11" s="45">
         <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="G11" s="36">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="24" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="B19" s="39">
         <f>Quizzes!K18</f>
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="C19" s="40">
         <f>Presentations!L18</f>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="F19" s="45">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="G19" s="36">
         <f t="shared" si="1"/>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="B29" s="35">
         <f>AVERAGE(B$3:B$26)</f>
-        <v>0.85833333333333339</v>
+        <v>0.88125000000000009</v>
       </c>
       <c r="C29" s="42">
         <f t="shared" ref="C29:G29" si="2">AVERAGE(C$3:C$26)</f>
@@ -4235,11 +4235,11 @@
       </c>
       <c r="F29" s="47">
         <f t="shared" si="2"/>
-        <v>0.85833333333333339</v>
+        <v>0.88125000000000009</v>
       </c>
       <c r="G29" s="38">
         <f t="shared" si="2"/>
-        <v>0.875</v>
+        <v>0.89583333333333337</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="B30" s="35">
         <f>STDEV(B$3:B$26)</f>
-        <v>0.50554891963580295</v>
+        <v>0.52145542558263314</v>
       </c>
       <c r="C30" s="42">
         <f t="shared" ref="C30:G30" si="3">STDEV(C$3:C$26)</f>
@@ -4264,11 +4264,11 @@
       </c>
       <c r="F30" s="47">
         <f t="shared" si="3"/>
-        <v>0.50554891963580295</v>
+        <v>0.52145542558263314</v>
       </c>
       <c r="G30" s="38">
         <f t="shared" si="3"/>
-        <v>0.51604684654213995</v>
+        <v>0.53118339309644202</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="B31" s="35">
         <f>MEDIAN(B$3:B$26)</f>
-        <v>0.95</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="C31" s="42">
         <f t="shared" ref="C31:G31" si="4">MEDIAN(C$3:C$26)</f>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="F31" s="47">
         <f t="shared" si="4"/>
-        <v>0.95</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="G31" s="38">
         <f t="shared" si="4"/>
